--- a/Project_Up/backtest_results.xlsx
+++ b/Project_Up/backtest_results.xlsx
@@ -14131,10 +14131,8 @@
       <c r="K202" s="2" t="n">
         <v/>
       </c>
-      <c r="L202" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L202" s="2" t="n">
+        <v/>
       </c>
       <c r="M202" s="4" t="n">
         <v/>
@@ -14142,10 +14140,8 @@
       <c r="N202" s="2" t="n">
         <v/>
       </c>
-      <c r="O202" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O202" s="2" t="n">
+        <v/>
       </c>
       <c r="P202" s="4" t="n">
         <v/>
@@ -14199,10 +14195,8 @@
       <c r="K203" s="5" t="n">
         <v/>
       </c>
-      <c r="L203" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L203" s="5" t="n">
+        <v/>
       </c>
       <c r="M203" s="4" t="n">
         <v/>
@@ -14210,10 +14204,8 @@
       <c r="N203" s="5" t="n">
         <v/>
       </c>
-      <c r="O203" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O203" s="5" t="n">
+        <v/>
       </c>
       <c r="P203" s="4" t="n">
         <v/>
@@ -14267,10 +14259,8 @@
       <c r="K204" s="2" t="n">
         <v/>
       </c>
-      <c r="L204" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L204" s="2" t="n">
+        <v/>
       </c>
       <c r="M204" s="4" t="n">
         <v/>
@@ -14278,10 +14268,8 @@
       <c r="N204" s="2" t="n">
         <v/>
       </c>
-      <c r="O204" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O204" s="2" t="n">
+        <v/>
       </c>
       <c r="P204" s="4" t="n">
         <v/>
@@ -14335,10 +14323,8 @@
       <c r="K205" s="5" t="n">
         <v/>
       </c>
-      <c r="L205" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L205" s="5" t="n">
+        <v/>
       </c>
       <c r="M205" s="4" t="n">
         <v/>
@@ -14346,10 +14332,8 @@
       <c r="N205" s="5" t="n">
         <v/>
       </c>
-      <c r="O205" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O205" s="5" t="n">
+        <v/>
       </c>
       <c r="P205" s="4" t="n">
         <v/>
@@ -14403,10 +14387,8 @@
       <c r="K206" s="2" t="n">
         <v/>
       </c>
-      <c r="L206" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L206" s="2" t="n">
+        <v/>
       </c>
       <c r="M206" s="4" t="n">
         <v/>
@@ -14414,10 +14396,8 @@
       <c r="N206" s="2" t="n">
         <v/>
       </c>
-      <c r="O206" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O206" s="2" t="n">
+        <v/>
       </c>
       <c r="P206" s="4" t="n">
         <v/>
@@ -14471,10 +14451,8 @@
       <c r="K207" s="5" t="n">
         <v/>
       </c>
-      <c r="L207" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L207" s="5" t="n">
+        <v/>
       </c>
       <c r="M207" s="4" t="n">
         <v/>
@@ -14482,10 +14460,8 @@
       <c r="N207" s="5" t="n">
         <v/>
       </c>
-      <c r="O207" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O207" s="5" t="n">
+        <v/>
       </c>
       <c r="P207" s="4" t="n">
         <v/>
@@ -14539,10 +14515,8 @@
       <c r="K208" s="2" t="n">
         <v/>
       </c>
-      <c r="L208" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L208" s="2" t="n">
+        <v/>
       </c>
       <c r="M208" s="4" t="n">
         <v/>
@@ -14550,10 +14524,8 @@
       <c r="N208" s="2" t="n">
         <v/>
       </c>
-      <c r="O208" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O208" s="2" t="n">
+        <v/>
       </c>
       <c r="P208" s="4" t="n">
         <v/>
@@ -14607,10 +14579,8 @@
       <c r="K209" s="5" t="n">
         <v/>
       </c>
-      <c r="L209" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L209" s="5" t="n">
+        <v/>
       </c>
       <c r="M209" s="4" t="n">
         <v/>
@@ -14618,10 +14588,8 @@
       <c r="N209" s="5" t="n">
         <v/>
       </c>
-      <c r="O209" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O209" s="5" t="n">
+        <v/>
       </c>
       <c r="P209" s="4" t="n">
         <v/>
@@ -14675,10 +14643,8 @@
       <c r="K210" s="2" t="n">
         <v/>
       </c>
-      <c r="L210" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L210" s="2" t="n">
+        <v/>
       </c>
       <c r="M210" s="4" t="n">
         <v/>
@@ -14686,10 +14652,8 @@
       <c r="N210" s="2" t="n">
         <v/>
       </c>
-      <c r="O210" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O210" s="2" t="n">
+        <v/>
       </c>
       <c r="P210" s="4" t="n">
         <v/>
@@ -14743,10 +14707,8 @@
       <c r="K211" s="5" t="n">
         <v/>
       </c>
-      <c r="L211" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L211" s="5" t="n">
+        <v/>
       </c>
       <c r="M211" s="4" t="n">
         <v/>
@@ -14754,10 +14716,8 @@
       <c r="N211" s="5" t="n">
         <v/>
       </c>
-      <c r="O211" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O211" s="5" t="n">
+        <v/>
       </c>
       <c r="P211" s="4" t="n">
         <v/>
@@ -14811,10 +14771,8 @@
       <c r="K212" s="2" t="n">
         <v/>
       </c>
-      <c r="L212" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L212" s="2" t="n">
+        <v/>
       </c>
       <c r="M212" s="4" t="n">
         <v/>
@@ -14822,10 +14780,8 @@
       <c r="N212" s="2" t="n">
         <v/>
       </c>
-      <c r="O212" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O212" s="2" t="n">
+        <v/>
       </c>
       <c r="P212" s="4" t="n">
         <v/>
@@ -14879,10 +14835,8 @@
       <c r="K213" s="5" t="n">
         <v/>
       </c>
-      <c r="L213" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L213" s="5" t="n">
+        <v/>
       </c>
       <c r="M213" s="4" t="n">
         <v/>
@@ -14890,10 +14844,8 @@
       <c r="N213" s="5" t="n">
         <v/>
       </c>
-      <c r="O213" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O213" s="5" t="n">
+        <v/>
       </c>
       <c r="P213" s="4" t="n">
         <v/>
@@ -14947,10 +14899,8 @@
       <c r="K214" s="2" t="n">
         <v/>
       </c>
-      <c r="L214" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L214" s="2" t="n">
+        <v/>
       </c>
       <c r="M214" s="4" t="n">
         <v/>
@@ -14958,10 +14908,8 @@
       <c r="N214" s="2" t="n">
         <v/>
       </c>
-      <c r="O214" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O214" s="2" t="n">
+        <v/>
       </c>
       <c r="P214" s="4" t="n">
         <v/>
@@ -15015,10 +14963,8 @@
       <c r="K215" s="5" t="n">
         <v/>
       </c>
-      <c r="L215" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L215" s="5" t="n">
+        <v/>
       </c>
       <c r="M215" s="4" t="n">
         <v/>
@@ -15026,10 +14972,8 @@
       <c r="N215" s="5" t="n">
         <v/>
       </c>
-      <c r="O215" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O215" s="5" t="n">
+        <v/>
       </c>
       <c r="P215" s="4" t="n">
         <v/>
@@ -15083,10 +15027,8 @@
       <c r="K216" s="2" t="n">
         <v/>
       </c>
-      <c r="L216" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L216" s="2" t="n">
+        <v/>
       </c>
       <c r="M216" s="4" t="n">
         <v/>
@@ -15094,10 +15036,8 @@
       <c r="N216" s="2" t="n">
         <v/>
       </c>
-      <c r="O216" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O216" s="2" t="n">
+        <v/>
       </c>
       <c r="P216" s="4" t="n">
         <v/>
@@ -15151,10 +15091,8 @@
       <c r="K217" s="5" t="n">
         <v/>
       </c>
-      <c r="L217" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L217" s="5" t="n">
+        <v/>
       </c>
       <c r="M217" s="4" t="n">
         <v/>
@@ -15162,10 +15100,8 @@
       <c r="N217" s="5" t="n">
         <v/>
       </c>
-      <c r="O217" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O217" s="5" t="n">
+        <v/>
       </c>
       <c r="P217" s="4" t="n">
         <v/>
@@ -15219,10 +15155,8 @@
       <c r="K218" s="2" t="n">
         <v/>
       </c>
-      <c r="L218" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L218" s="2" t="n">
+        <v/>
       </c>
       <c r="M218" s="4" t="n">
         <v/>
@@ -15230,10 +15164,8 @@
       <c r="N218" s="2" t="n">
         <v/>
       </c>
-      <c r="O218" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O218" s="2" t="n">
+        <v/>
       </c>
       <c r="P218" s="4" t="n">
         <v/>
@@ -15287,10 +15219,8 @@
       <c r="K219" s="5" t="n">
         <v/>
       </c>
-      <c r="L219" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L219" s="5" t="n">
+        <v/>
       </c>
       <c r="M219" s="4" t="n">
         <v/>
@@ -15298,10 +15228,8 @@
       <c r="N219" s="5" t="n">
         <v/>
       </c>
-      <c r="O219" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O219" s="5" t="n">
+        <v/>
       </c>
       <c r="P219" s="4" t="n">
         <v/>
@@ -15355,10 +15283,8 @@
       <c r="K220" s="2" t="n">
         <v/>
       </c>
-      <c r="L220" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L220" s="2" t="n">
+        <v/>
       </c>
       <c r="M220" s="4" t="n">
         <v/>
@@ -15366,10 +15292,8 @@
       <c r="N220" s="2" t="n">
         <v/>
       </c>
-      <c r="O220" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O220" s="2" t="n">
+        <v/>
       </c>
       <c r="P220" s="4" t="n">
         <v/>
@@ -15423,10 +15347,8 @@
       <c r="K221" s="5" t="n">
         <v/>
       </c>
-      <c r="L221" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L221" s="5" t="n">
+        <v/>
       </c>
       <c r="M221" s="4" t="n">
         <v/>
@@ -15434,10 +15356,8 @@
       <c r="N221" s="5" t="n">
         <v/>
       </c>
-      <c r="O221" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O221" s="5" t="n">
+        <v/>
       </c>
       <c r="P221" s="4" t="n">
         <v/>
@@ -15491,10 +15411,8 @@
       <c r="K222" s="2" t="n">
         <v/>
       </c>
-      <c r="L222" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L222" s="2" t="n">
+        <v/>
       </c>
       <c r="M222" s="4" t="n">
         <v/>
@@ -15502,10 +15420,8 @@
       <c r="N222" s="2" t="n">
         <v/>
       </c>
-      <c r="O222" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O222" s="2" t="n">
+        <v/>
       </c>
       <c r="P222" s="4" t="n">
         <v/>
@@ -15559,10 +15475,8 @@
       <c r="K223" s="5" t="n">
         <v/>
       </c>
-      <c r="L223" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L223" s="5" t="n">
+        <v/>
       </c>
       <c r="M223" s="4" t="n">
         <v/>
@@ -15570,10 +15484,8 @@
       <c r="N223" s="5" t="n">
         <v/>
       </c>
-      <c r="O223" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O223" s="5" t="n">
+        <v/>
       </c>
       <c r="P223" s="4" t="n">
         <v/>
@@ -15627,10 +15539,8 @@
       <c r="K224" s="2" t="n">
         <v/>
       </c>
-      <c r="L224" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L224" s="2" t="n">
+        <v/>
       </c>
       <c r="M224" s="4" t="n">
         <v/>
@@ -15638,10 +15548,8 @@
       <c r="N224" s="2" t="n">
         <v/>
       </c>
-      <c r="O224" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O224" s="2" t="n">
+        <v/>
       </c>
       <c r="P224" s="4" t="n">
         <v/>
@@ -15695,10 +15603,8 @@
       <c r="K225" s="5" t="n">
         <v/>
       </c>
-      <c r="L225" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L225" s="5" t="n">
+        <v/>
       </c>
       <c r="M225" s="4" t="n">
         <v/>
@@ -15706,10 +15612,8 @@
       <c r="N225" s="5" t="n">
         <v/>
       </c>
-      <c r="O225" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O225" s="5" t="n">
+        <v/>
       </c>
       <c r="P225" s="4" t="n">
         <v/>
@@ -15763,10 +15667,8 @@
       <c r="K226" s="2" t="n">
         <v/>
       </c>
-      <c r="L226" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L226" s="2" t="n">
+        <v/>
       </c>
       <c r="M226" s="4" t="n">
         <v/>
@@ -15774,10 +15676,8 @@
       <c r="N226" s="2" t="n">
         <v/>
       </c>
-      <c r="O226" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O226" s="2" t="n">
+        <v/>
       </c>
       <c r="P226" s="4" t="n">
         <v/>
@@ -15831,10 +15731,8 @@
       <c r="K227" s="5" t="n">
         <v/>
       </c>
-      <c r="L227" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L227" s="5" t="n">
+        <v/>
       </c>
       <c r="M227" s="4" t="n">
         <v/>
@@ -15842,10 +15740,8 @@
       <c r="N227" s="5" t="n">
         <v/>
       </c>
-      <c r="O227" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O227" s="5" t="n">
+        <v/>
       </c>
       <c r="P227" s="4" t="n">
         <v/>
@@ -15899,10 +15795,8 @@
       <c r="K228" s="2" t="n">
         <v/>
       </c>
-      <c r="L228" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L228" s="2" t="n">
+        <v/>
       </c>
       <c r="M228" s="4" t="n">
         <v/>
@@ -15910,10 +15804,8 @@
       <c r="N228" s="2" t="n">
         <v/>
       </c>
-      <c r="O228" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O228" s="2" t="n">
+        <v/>
       </c>
       <c r="P228" s="4" t="n">
         <v/>
@@ -15967,10 +15859,8 @@
       <c r="K229" s="5" t="n">
         <v/>
       </c>
-      <c r="L229" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L229" s="5" t="n">
+        <v/>
       </c>
       <c r="M229" s="4" t="n">
         <v/>
@@ -15978,10 +15868,8 @@
       <c r="N229" s="5" t="n">
         <v/>
       </c>
-      <c r="O229" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O229" s="5" t="n">
+        <v/>
       </c>
       <c r="P229" s="4" t="n">
         <v/>
@@ -16035,10 +15923,8 @@
       <c r="K230" s="2" t="n">
         <v/>
       </c>
-      <c r="L230" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L230" s="2" t="n">
+        <v/>
       </c>
       <c r="M230" s="4" t="n">
         <v/>
@@ -16046,10 +15932,8 @@
       <c r="N230" s="2" t="n">
         <v/>
       </c>
-      <c r="O230" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O230" s="2" t="n">
+        <v/>
       </c>
       <c r="P230" s="4" t="n">
         <v/>
@@ -16103,10 +15987,8 @@
       <c r="K231" s="5" t="n">
         <v/>
       </c>
-      <c r="L231" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L231" s="5" t="n">
+        <v/>
       </c>
       <c r="M231" s="4" t="n">
         <v/>
@@ -16114,10 +15996,8 @@
       <c r="N231" s="5" t="n">
         <v/>
       </c>
-      <c r="O231" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O231" s="5" t="n">
+        <v/>
       </c>
       <c r="P231" s="4" t="n">
         <v/>
@@ -16160,10 +16040,8 @@
       <c r="H232" s="2" t="n">
         <v/>
       </c>
-      <c r="I232" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I232" s="2" t="n">
+        <v/>
       </c>
       <c r="J232" s="4" t="n">
         <v/>
@@ -16171,10 +16049,8 @@
       <c r="K232" s="2" t="n">
         <v/>
       </c>
-      <c r="L232" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L232" s="2" t="n">
+        <v/>
       </c>
       <c r="M232" s="4" t="n">
         <v/>
@@ -16182,10 +16058,8 @@
       <c r="N232" s="2" t="n">
         <v/>
       </c>
-      <c r="O232" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O232" s="2" t="n">
+        <v/>
       </c>
       <c r="P232" s="4" t="n">
         <v/>
@@ -16228,10 +16102,8 @@
       <c r="H233" s="5" t="n">
         <v/>
       </c>
-      <c r="I233" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I233" s="5" t="n">
+        <v/>
       </c>
       <c r="J233" s="4" t="n">
         <v/>
@@ -16239,10 +16111,8 @@
       <c r="K233" s="5" t="n">
         <v/>
       </c>
-      <c r="L233" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L233" s="5" t="n">
+        <v/>
       </c>
       <c r="M233" s="4" t="n">
         <v/>
@@ -16250,10 +16120,8 @@
       <c r="N233" s="5" t="n">
         <v/>
       </c>
-      <c r="O233" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O233" s="5" t="n">
+        <v/>
       </c>
       <c r="P233" s="4" t="n">
         <v/>
@@ -16296,10 +16164,8 @@
       <c r="H234" s="2" t="n">
         <v/>
       </c>
-      <c r="I234" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I234" s="2" t="n">
+        <v/>
       </c>
       <c r="J234" s="4" t="n">
         <v/>
@@ -16307,10 +16173,8 @@
       <c r="K234" s="2" t="n">
         <v/>
       </c>
-      <c r="L234" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L234" s="2" t="n">
+        <v/>
       </c>
       <c r="M234" s="4" t="n">
         <v/>
@@ -16318,10 +16182,8 @@
       <c r="N234" s="2" t="n">
         <v/>
       </c>
-      <c r="O234" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O234" s="2" t="n">
+        <v/>
       </c>
       <c r="P234" s="4" t="n">
         <v/>
@@ -16364,10 +16226,8 @@
       <c r="H235" s="5" t="n">
         <v/>
       </c>
-      <c r="I235" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I235" s="5" t="n">
+        <v/>
       </c>
       <c r="J235" s="4" t="n">
         <v/>
@@ -16375,10 +16235,8 @@
       <c r="K235" s="5" t="n">
         <v/>
       </c>
-      <c r="L235" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L235" s="5" t="n">
+        <v/>
       </c>
       <c r="M235" s="4" t="n">
         <v/>
@@ -16386,10 +16244,8 @@
       <c r="N235" s="5" t="n">
         <v/>
       </c>
-      <c r="O235" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O235" s="5" t="n">
+        <v/>
       </c>
       <c r="P235" s="4" t="n">
         <v/>
@@ -16432,10 +16288,8 @@
       <c r="H236" s="2" t="n">
         <v/>
       </c>
-      <c r="I236" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I236" s="2" t="n">
+        <v/>
       </c>
       <c r="J236" s="4" t="n">
         <v/>
@@ -16443,10 +16297,8 @@
       <c r="K236" s="2" t="n">
         <v/>
       </c>
-      <c r="L236" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L236" s="2" t="n">
+        <v/>
       </c>
       <c r="M236" s="4" t="n">
         <v/>
@@ -16454,10 +16306,8 @@
       <c r="N236" s="2" t="n">
         <v/>
       </c>
-      <c r="O236" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O236" s="2" t="n">
+        <v/>
       </c>
       <c r="P236" s="4" t="n">
         <v/>
@@ -16500,10 +16350,8 @@
       <c r="H237" s="5" t="n">
         <v/>
       </c>
-      <c r="I237" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I237" s="5" t="n">
+        <v/>
       </c>
       <c r="J237" s="4" t="n">
         <v/>
@@ -16511,10 +16359,8 @@
       <c r="K237" s="5" t="n">
         <v/>
       </c>
-      <c r="L237" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L237" s="5" t="n">
+        <v/>
       </c>
       <c r="M237" s="4" t="n">
         <v/>
@@ -16522,10 +16368,8 @@
       <c r="N237" s="5" t="n">
         <v/>
       </c>
-      <c r="O237" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O237" s="5" t="n">
+        <v/>
       </c>
       <c r="P237" s="4" t="n">
         <v/>
@@ -16568,10 +16412,8 @@
       <c r="H238" s="2" t="n">
         <v/>
       </c>
-      <c r="I238" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I238" s="2" t="n">
+        <v/>
       </c>
       <c r="J238" s="4" t="n">
         <v/>
@@ -16579,10 +16421,8 @@
       <c r="K238" s="2" t="n">
         <v/>
       </c>
-      <c r="L238" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L238" s="2" t="n">
+        <v/>
       </c>
       <c r="M238" s="4" t="n">
         <v/>
@@ -16590,10 +16430,8 @@
       <c r="N238" s="2" t="n">
         <v/>
       </c>
-      <c r="O238" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O238" s="2" t="n">
+        <v/>
       </c>
       <c r="P238" s="4" t="n">
         <v/>
@@ -16636,10 +16474,8 @@
       <c r="H239" s="5" t="n">
         <v/>
       </c>
-      <c r="I239" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I239" s="5" t="n">
+        <v/>
       </c>
       <c r="J239" s="4" t="n">
         <v/>
@@ -16647,10 +16483,8 @@
       <c r="K239" s="5" t="n">
         <v/>
       </c>
-      <c r="L239" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L239" s="5" t="n">
+        <v/>
       </c>
       <c r="M239" s="4" t="n">
         <v/>
@@ -16658,10 +16492,8 @@
       <c r="N239" s="5" t="n">
         <v/>
       </c>
-      <c r="O239" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O239" s="5" t="n">
+        <v/>
       </c>
       <c r="P239" s="4" t="n">
         <v/>
@@ -16704,10 +16536,8 @@
       <c r="H240" s="2" t="n">
         <v/>
       </c>
-      <c r="I240" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I240" s="2" t="n">
+        <v/>
       </c>
       <c r="J240" s="4" t="n">
         <v/>
@@ -16715,10 +16545,8 @@
       <c r="K240" s="2" t="n">
         <v/>
       </c>
-      <c r="L240" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L240" s="2" t="n">
+        <v/>
       </c>
       <c r="M240" s="4" t="n">
         <v/>
@@ -16726,10 +16554,8 @@
       <c r="N240" s="2" t="n">
         <v/>
       </c>
-      <c r="O240" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O240" s="2" t="n">
+        <v/>
       </c>
       <c r="P240" s="4" t="n">
         <v/>
@@ -16772,10 +16598,8 @@
       <c r="H241" s="5" t="n">
         <v/>
       </c>
-      <c r="I241" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I241" s="5" t="n">
+        <v/>
       </c>
       <c r="J241" s="4" t="n">
         <v/>
@@ -16783,10 +16607,8 @@
       <c r="K241" s="5" t="n">
         <v/>
       </c>
-      <c r="L241" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L241" s="5" t="n">
+        <v/>
       </c>
       <c r="M241" s="4" t="n">
         <v/>
@@ -16794,10 +16616,8 @@
       <c r="N241" s="5" t="n">
         <v/>
       </c>
-      <c r="O241" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O241" s="5" t="n">
+        <v/>
       </c>
       <c r="P241" s="4" t="n">
         <v/>
@@ -16840,10 +16660,8 @@
       <c r="H242" s="2" t="n">
         <v/>
       </c>
-      <c r="I242" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I242" s="2" t="n">
+        <v/>
       </c>
       <c r="J242" s="4" t="n">
         <v/>
@@ -16851,10 +16669,8 @@
       <c r="K242" s="2" t="n">
         <v/>
       </c>
-      <c r="L242" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L242" s="2" t="n">
+        <v/>
       </c>
       <c r="M242" s="4" t="n">
         <v/>
@@ -16862,10 +16678,8 @@
       <c r="N242" s="2" t="n">
         <v/>
       </c>
-      <c r="O242" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O242" s="2" t="n">
+        <v/>
       </c>
       <c r="P242" s="4" t="n">
         <v/>
@@ -16908,10 +16722,8 @@
       <c r="H243" s="5" t="n">
         <v/>
       </c>
-      <c r="I243" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I243" s="5" t="n">
+        <v/>
       </c>
       <c r="J243" s="4" t="n">
         <v/>
@@ -16919,10 +16731,8 @@
       <c r="K243" s="5" t="n">
         <v/>
       </c>
-      <c r="L243" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L243" s="5" t="n">
+        <v/>
       </c>
       <c r="M243" s="4" t="n">
         <v/>
@@ -16930,10 +16740,8 @@
       <c r="N243" s="5" t="n">
         <v/>
       </c>
-      <c r="O243" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O243" s="5" t="n">
+        <v/>
       </c>
       <c r="P243" s="4" t="n">
         <v/>
@@ -16976,10 +16784,8 @@
       <c r="H244" s="2" t="n">
         <v/>
       </c>
-      <c r="I244" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I244" s="2" t="n">
+        <v/>
       </c>
       <c r="J244" s="4" t="n">
         <v/>
@@ -16987,10 +16793,8 @@
       <c r="K244" s="2" t="n">
         <v/>
       </c>
-      <c r="L244" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L244" s="2" t="n">
+        <v/>
       </c>
       <c r="M244" s="4" t="n">
         <v/>
@@ -16998,10 +16802,8 @@
       <c r="N244" s="2" t="n">
         <v/>
       </c>
-      <c r="O244" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O244" s="2" t="n">
+        <v/>
       </c>
       <c r="P244" s="4" t="n">
         <v/>
@@ -17044,10 +16846,8 @@
       <c r="H245" s="5" t="n">
         <v/>
       </c>
-      <c r="I245" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I245" s="5" t="n">
+        <v/>
       </c>
       <c r="J245" s="4" t="n">
         <v/>
@@ -17055,10 +16855,8 @@
       <c r="K245" s="5" t="n">
         <v/>
       </c>
-      <c r="L245" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L245" s="5" t="n">
+        <v/>
       </c>
       <c r="M245" s="4" t="n">
         <v/>
@@ -17066,10 +16864,8 @@
       <c r="N245" s="5" t="n">
         <v/>
       </c>
-      <c r="O245" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O245" s="5" t="n">
+        <v/>
       </c>
       <c r="P245" s="4" t="n">
         <v/>
@@ -17112,10 +16908,8 @@
       <c r="H246" s="2" t="n">
         <v/>
       </c>
-      <c r="I246" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I246" s="2" t="n">
+        <v/>
       </c>
       <c r="J246" s="4" t="n">
         <v/>
@@ -17123,10 +16917,8 @@
       <c r="K246" s="2" t="n">
         <v/>
       </c>
-      <c r="L246" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="L246" s="2" t="n">
+        <v/>
       </c>
       <c r="M246" s="4" t="n">
         <v/>
@@ -17134,10 +16926,8 @@
       <c r="N246" s="2" t="n">
         <v/>
       </c>
-      <c r="O246" s="2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="O246" s="2" t="n">
+        <v/>
       </c>
       <c r="P246" s="4" t="n">
         <v/>
